--- a/results/Int All Data 0.4/Linea_fi_explain.xlsx
+++ b/results/Int All Data 0.4/Linea_fi_explain.xlsx
@@ -1685,7 +1685,7 @@
         <v>0.002696765406437673</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0004512986266774465</v>
+        <v>0.0004559978747977468</v>
       </c>
       <c r="F3" t="n">
         <v>-0.000886510438567758</v>
@@ -1826,7 +1826,7 @@
         <v>0.007075560189244272</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.0009861513666654174</v>
+        <v>0.00098174219558958</v>
       </c>
       <c r="BA3" t="n">
         <v>0.01794857170937703</v>
@@ -1844,7 +1844,7 @@
         <v>0.007598416132129254</v>
       </c>
       <c r="BF3" t="n">
-        <v>-0.0007723203283411872</v>
+        <v>-0.000763729263049091</v>
       </c>
       <c r="BG3" t="n">
         <v>0.001165526442297462</v>
@@ -1883,7 +1883,7 @@
         <v>0.03377588980933793</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.0006040846121917853</v>
+        <v>0.0006040846121917863</v>
       </c>
       <c r="BT3" t="n">
         <v>-0.0002118692029447811</v>
@@ -1895,13 +1895,13 @@
         <v>0.003868491268624011</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.920962980368146e-05</v>
+        <v>2.820243555907819e-05</v>
       </c>
       <c r="BX3" t="n">
-        <v>-0.004029564094155577</v>
+        <v>-0.004033867020145251</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.001443908504027516</v>
+        <v>0.001448574859603811</v>
       </c>
       <c r="BZ3" t="n">
         <v>0.001448574859603811</v>
@@ -1910,10 +1910,10 @@
         <v>0.004733682230846505</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.0229263184313934</v>
+        <v>0.02293077840732992</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.004122676156443393</v>
+        <v>0.004118179753565694</v>
       </c>
       <c r="CD3" t="n">
         <v>-0.0003964044079373209</v>
@@ -1922,7 +1922,7 @@
         <v>8.119663184136373e-05</v>
       </c>
       <c r="CF3" t="n">
-        <v>-0.0004581282327026426</v>
+        <v>-0.000436166199187823</v>
       </c>
       <c r="CG3" t="n">
         <v>0.4362258512331202</v>
@@ -1934,7 +1934,7 @@
         <v>0.3012398622956619</v>
       </c>
       <c r="CJ3" t="n">
-        <v>2.820243555907819e-05</v>
+        <v>1.920962980368146e-05</v>
       </c>
       <c r="CK3" t="n">
         <v>-0.0003895386539853406</v>
@@ -1958,7 +1958,7 @@
         <v>0.06817923384745163</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.04147173648583637</v>
+        <v>0.04147158413161202</v>
       </c>
       <c r="CS3" t="n">
         <v>0.3462150212789077</v>
@@ -2027,7 +2027,7 @@
         <v>0.008711334779690027</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.01054042515266679</v>
+        <v>0.01054468228336071</v>
       </c>
       <c r="DP3" t="n">
         <v>0.007985316050426185</v>
@@ -2066,7 +2066,7 @@
         <v>0.006186578684745022</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.01054042515266679</v>
+        <v>0.01054468228336071</v>
       </c>
       <c r="EC3" t="n">
         <v>0.004760278656997291</v>
@@ -2120,7 +2120,7 @@
         <v>-0.0002921648608383187</v>
       </c>
       <c r="ET3" t="n">
-        <v>0.00550368344089786</v>
+        <v>0.005499187038020163</v>
       </c>
       <c r="EU3" t="n">
         <v>0.04508019979470489</v>
@@ -2154,7 +2154,7 @@
         <v>0.005355400060374912</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003413717953530888</v>
+        <v>0.00340996727506167</v>
       </c>
       <c r="F4" t="n">
         <v>0.002531218833352766</v>
@@ -2295,7 +2295,7 @@
         <v>0.0186485526858006</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.003783633247003555</v>
+        <v>0.003783565646512397</v>
       </c>
       <c r="BA4" t="n">
         <v>0.01950650470771237</v>
@@ -2313,7 +2313,7 @@
         <v>0.0116543848961882</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.004023126818167736</v>
+        <v>0.004019341742170221</v>
       </c>
       <c r="BG4" t="n">
         <v>0.006079186474566923</v>
@@ -2352,7 +2352,7 @@
         <v>0.03932589234090792</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.00685334507194933</v>
+        <v>0.006853345071949329</v>
       </c>
       <c r="BT4" t="n">
         <v>0.002916596897648244</v>
@@ -2364,13 +2364,13 @@
         <v>0.007822055170154614</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.0003711744021958174</v>
+        <v>0.0003777407385258786</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.0104810175243851</v>
+        <v>0.01049092124829963</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.004419127784898627</v>
+        <v>0.00440972871280706</v>
       </c>
       <c r="BZ4" t="n">
         <v>0.00440972871280706</v>
@@ -2379,10 +2379,10 @@
         <v>0.01188061620521522</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.02778991584342852</v>
+        <v>0.02777663692300756</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.0152966363551525</v>
+        <v>0.01529672649982525</v>
       </c>
       <c r="CD4" t="n">
         <v>0.004422767371452796</v>
@@ -2391,7 +2391,7 @@
         <v>0.002000330062984381</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.002991947215919242</v>
+        <v>0.002988614653006702</v>
       </c>
       <c r="CG4" t="n">
         <v>0.1287412555063921</v>
@@ -2403,7 +2403,7 @@
         <v>0.07452462157804463</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.0003777407385258786</v>
+        <v>0.0003711744021958174</v>
       </c>
       <c r="CK4" t="n">
         <v>0.006163631631604017</v>
@@ -2427,7 +2427,7 @@
         <v>0.04142990209961489</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.03175212880229007</v>
+        <v>0.03174896804681829</v>
       </c>
       <c r="CS4" t="n">
         <v>0.09100173999645671</v>
@@ -2496,7 +2496,7 @@
         <v>0.01298056464915402</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.02553516877095756</v>
+        <v>0.02553751752882948</v>
       </c>
       <c r="DP4" t="n">
         <v>0.01997962800194515</v>
@@ -2535,7 +2535,7 @@
         <v>0.01008291635734304</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.02553516877095756</v>
+        <v>0.02553751752882948</v>
       </c>
       <c r="EC4" t="n">
         <v>0.01162400460366655</v>
@@ -2589,7 +2589,7 @@
         <v>0.00133216661111206</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.01891185308671728</v>
+        <v>0.01891331230086638</v>
       </c>
       <c r="EU4" t="n">
         <v>0.05225639047318026</v>
@@ -2836,10 +2836,10 @@
         <v>-0.0004666355576294912</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0.02573149741824443</v>
+        <v>-0.02577452667814116</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.006579561362575826</v>
+        <v>-0.006532897806812876</v>
       </c>
       <c r="BZ5" t="n">
         <v>-0.006532897806812876</v>
@@ -2860,7 +2860,7 @@
         <v>-0.00206834532374095</v>
       </c>
       <c r="CF5" t="n">
-        <v>-0.007745266781411364</v>
+        <v>-0.007702237521514632</v>
       </c>
       <c r="CG5" t="n">
         <v>0.2448436770881941</v>
@@ -3251,7 +3251,7 @@
         <v>0.002040039700164567</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0.003893112952546565</v>
+        <v>-0.003871635289316324</v>
       </c>
       <c r="BG6" t="n">
         <v>-0.00199087435398686</v>
@@ -3702,7 +3702,7 @@
         <v>0.001659566454619804</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.001196054057499818</v>
+        <v>0.00117400820212063</v>
       </c>
       <c r="BA7" t="n">
         <v>0.01215056707971063</v>
@@ -3771,7 +3771,7 @@
         <v>0.0003873246259979924</v>
       </c>
       <c r="BW7" t="n">
-        <v>2.422665042570716e-05</v>
+        <v>6.919067920269084e-05</v>
       </c>
       <c r="BX7" t="n">
         <v>-0.0005776340110905609</v>
@@ -3786,7 +3786,7 @@
         <v>0.002921255866892803</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.01074616416271733</v>
+        <v>0.01076966040331883</v>
       </c>
       <c r="CC7" t="n">
         <v>0.002044493017345422</v>
@@ -3810,7 +3810,7 @@
         <v>0.2920092068318011</v>
       </c>
       <c r="CJ7" t="n">
-        <v>6.919067920269084e-05</v>
+        <v>2.422665042570716e-05</v>
       </c>
       <c r="CK7" t="n">
         <v>0.001119610019023459</v>
@@ -3834,7 +3834,7 @@
         <v>0.0606849620678209</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.03603808153200489</v>
+        <v>0.03605980177527161</v>
       </c>
       <c r="CS7" t="n">
         <v>0.3640168792800811</v>
@@ -3996,7 +3996,7 @@
         <v>-9.297073619299323e-05</v>
       </c>
       <c r="ET7" t="n">
-        <v>1.665334536937735e-17</v>
+        <v>-2.248201438847519e-05</v>
       </c>
       <c r="EU7" t="n">
         <v>0.01780582922824304</v>
@@ -4228,7 +4228,7 @@
         <v>0.06021902478438881</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.001721479958890035</v>
+        <v>0.001721479958890038</v>
       </c>
       <c r="BT8" t="n">
         <v>0.0007907250165644197</v>
@@ -4255,10 +4255,10 @@
         <v>0.006124494734109609</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.03875927446329742</v>
+        <v>0.03876991729003221</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.003551787154116875</v>
+        <v>0.003518064132534138</v>
       </c>
       <c r="CD8" t="n">
         <v>0.0007037683431546315</v>
@@ -4267,7 +4267,7 @@
         <v>0.001875345617569266</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.0005045368467131133</v>
+        <v>0.0005830058175681829</v>
       </c>
       <c r="CG8" t="n">
         <v>0.549196310245037</v>
@@ -4303,7 +4303,7 @@
         <v>0.08577960644423467</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.05709767055697488</v>
+        <v>0.05706394753539214</v>
       </c>
       <c r="CS8" t="n">
         <v>0.4033464265430411</v>
@@ -4724,7 +4724,7 @@
         <v>0.03294172932330827</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.08147482014388494</v>
+        <v>0.08142985611510795</v>
       </c>
       <c r="CC9" t="n">
         <v>0.03793900184842883</v>
